--- a/data/availability/projects/la-vista-developments/el-patio-town.xlsx
+++ b/data/availability/projects/la-vista-developments/el-patio-town.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Jan 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Sep 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Sep 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Jan 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Sep 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Jan 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Jan 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Jan 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Jan 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Jan 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Sep 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Sep 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Jan 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Sep 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Jan 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Jan 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
